--- a/mmkBelgeler/KU008 CPL Kenar Kesme payları.xlsx
+++ b/mmkBelgeler/KU008 CPL Kenar Kesme payları.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\myilmaz\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/mmkBelgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A1FAB6-ECD2-EE45-AB93-F5ADDD92B7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26760" windowHeight="12390"/>
+    <workbookView xWindow="0" yWindow="10160" windowWidth="26760" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,22 +96,22 @@
     <t>Grade</t>
   </si>
   <si>
-    <t>Min Kalınlık</t>
-  </si>
-  <si>
-    <t>Min Genişlik</t>
-  </si>
-  <si>
     <t>Kenar Kesme
 Payı mm</t>
+  </si>
+  <si>
+    <t>HR Min Kalınlık</t>
+  </si>
+  <si>
+    <t>HR Max Kalınlık</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -264,6 +265,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -637,11 +639,11 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -970,18 +972,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="28" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -989,16 +991,16 @@
         <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,7 +1017,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1085,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,7 +1153,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,7 +1187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1236,7 +1238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +1255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1287,7 +1289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1304,7 +1306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,7 +1340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1372,7 +1374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,7 +1408,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>14</v>
       </c>
@@ -1457,7 +1459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
@@ -1474,7 +1476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -1491,7 +1493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>14</v>
       </c>
@@ -1508,7 +1510,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>14</v>
       </c>
@@ -1525,7 +1527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,7 +1544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>14</v>
       </c>
@@ -1559,7 +1561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1576,7 +1578,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>14</v>
       </c>
@@ -1593,7 +1595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>14</v>
       </c>
@@ -1610,7 +1612,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>14</v>
       </c>
@@ -1627,7 +1629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>14</v>
       </c>
@@ -1644,7 +1646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>14</v>
       </c>
@@ -1661,7 +1663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -1678,7 +1680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1695,7 +1697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -1712,7 +1714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -1729,7 +1731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>15</v>
       </c>
@@ -1746,7 +1748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>21</v>
       </c>
@@ -1763,7 +1765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -1780,7 +1782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -1797,7 +1799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>21</v>
       </c>
@@ -1814,7 +1816,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>21</v>
       </c>
@@ -1848,7 +1850,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>21</v>
       </c>
@@ -1865,7 +1867,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>21</v>
       </c>
@@ -1882,7 +1884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>21</v>
       </c>
@@ -1899,7 +1901,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
@@ -1916,7 +1918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
@@ -1933,7 +1935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>21</v>
       </c>
@@ -1950,7 +1952,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>21</v>
       </c>
@@ -1967,7 +1969,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>21</v>
       </c>
@@ -1984,7 +1986,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>21</v>
       </c>
@@ -2001,7 +2003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>21</v>
       </c>
@@ -2018,7 +2020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>21</v>
       </c>
@@ -2035,7 +2037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>21</v>
       </c>
@@ -2052,7 +2054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>21</v>
       </c>
@@ -2069,7 +2071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>21</v>
       </c>
@@ -2086,7 +2088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>21</v>
       </c>
@@ -2103,7 +2105,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>21</v>
       </c>
@@ -2120,7 +2122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>21</v>
       </c>
@@ -2137,7 +2139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>21</v>
       </c>
@@ -2161,18 +2163,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mmkBelgeler/KU008 CPL Kenar Kesme payları.xlsx
+++ b/mmkBelgeler/KU008 CPL Kenar Kesme payları.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/mmkBelgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A1FAB6-ECD2-EE45-AB93-F5ADDD92B7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4954CF-EE65-9F49-8251-B4A965AC4C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="10160" windowWidth="26760" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="7240" windowWidth="26760" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,14 +96,13 @@
     <t>Grade</t>
   </si>
   <si>
-    <t>Kenar Kesme
-Payı mm</t>
-  </si>
-  <si>
     <t>HR Min Kalınlık</t>
   </si>
   <si>
     <t>HR Max Kalınlık</t>
+  </si>
+  <si>
+    <t>Kenar Kesme Payı mm</t>
   </si>
 </sst>
 </file>
@@ -991,13 +990,13 @@
         <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
